--- a/Chitrich_1/Files/output.xlsx
+++ b/Chitrich_1/Files/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0181cd2e986c4bf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbbcc5bd6e9624561"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11,14 +11,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row>
-      <x:c r="A1" t="str">
+      <x:c t="str">
         <x:v>Id</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c t="str">
         <x:v>Name</x:v>
-      </x:c>
-      <x:c r="C1" t="str">
-        <x:v>Age</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28,9 +25,6 @@
       <x:c t="str">
         <x:v>John</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>28</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -38,9 +32,6 @@
       </x:c>
       <x:c t="str">
         <x:v>Jane</x:v>
-      </x:c>
-      <x:c t="n">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -50,9 +41,6 @@
       <x:c t="str">
         <x:v>Alex</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>35</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -60,9 +48,6 @@
       </x:c>
       <x:c t="str">
         <x:v>Emily</x:v>
-      </x:c>
-      <x:c t="n">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -72,9 +57,6 @@
       <x:c t="str">
         <x:v>Michael</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>40</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -82,9 +64,6 @@
       </x:c>
       <x:c t="str">
         <x:v>Sarah</x:v>
-      </x:c>
-      <x:c t="n">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -94,9 +73,6 @@
       <x:c t="str">
         <x:v>David</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>38</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -104,9 +80,6 @@
       </x:c>
       <x:c t="str">
         <x:v>Laura</x:v>
-      </x:c>
-      <x:c t="n">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -116,9 +89,6 @@
       <x:c t="str">
         <x:v>Robert</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>33</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -126,9 +96,6 @@
       </x:c>
       <x:c t="str">
         <x:v>Sophia</x:v>
-      </x:c>
-      <x:c t="n">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -138,9 +105,6 @@
       <x:c t="str">
         <x:v>Daniel</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -148,9 +112,6 @@
       </x:c>
       <x:c t="str">
         <x:v>Emma</x:v>
-      </x:c>
-      <x:c t="n">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -160,9 +121,6 @@
       <x:c t="str">
         <x:v>James</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>34</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -170,9 +128,6 @@
       </x:c>
       <x:c t="str">
         <x:v>Olivia</x:v>
-      </x:c>
-      <x:c t="n">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -182,9 +137,6 @@
       <x:c t="str">
         <x:v>William</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>32</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -192,9 +144,6 @@
       </x:c>
       <x:c t="str">
         <x:v>Isabella</x:v>
-      </x:c>
-      <x:c t="n">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -204,9 +153,6 @@
       <x:c t="str">
         <x:v>Joseph</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>36</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -214,9 +160,6 @@
       </x:c>
       <x:c t="str">
         <x:v>Mia</x:v>
-      </x:c>
-      <x:c t="n">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -226,9 +169,6 @@
       <x:c t="str">
         <x:v>Charles</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>37</x:v>
-      </x:c>
     </x:row>
     <x:row>
       <x:c t="n">
@@ -237,9 +177,6 @@
       <x:c t="str">
         <x:v>Ava</x:v>
       </x:c>
-      <x:c t="n">
-        <x:v>39</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
 </x:worksheet>
